--- a/Project-QM/Empleados_capsula.xlsx
+++ b/Project-QM/Empleados_capsula.xlsx
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Francisco\Downloads\Failures-PMI\Project-QM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jtinoco2\Downloads\Failures-PMI\Project-QM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{87791D84-DC78-45C6-91C4-5A86417E886B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6238F29-7617-4652-A348-39AA42CBD50A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{1C5DA410-3262-4A33-9547-24D9BD4D0618}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{1C5DA410-3262-4A33-9547-24D9BD4D0618}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$D$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$D$29</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -416,10 +416,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -440,14 +440,11 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -464,7 +461,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -781,18 +778,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A667A326-1335-4EA3-87C0-BA97F18477A6}">
   <dimension ref="A1:H29"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="17.33203125" customWidth="1"/>
-    <col min="3" max="3" width="31.88671875" customWidth="1"/>
-    <col min="4" max="4" width="23.21875" customWidth="1"/>
-    <col min="5" max="5" width="17.109375" style="2" customWidth="1"/>
-    <col min="6" max="6" width="11.5546875" style="1"/>
-    <col min="7" max="7" width="31.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.5546875" style="1"/>
+    <col min="2" max="2" width="17.36328125" customWidth="1"/>
+    <col min="3" max="3" width="31.90625" customWidth="1"/>
+    <col min="4" max="4" width="23.1796875" customWidth="1"/>
+    <col min="5" max="5" width="17.08984375" style="2" customWidth="1"/>
+    <col min="6" max="6" width="11.54296875" style="1"/>
+    <col min="7" max="7" width="31.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.54296875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -811,7 +808,7 @@
       <c r="F1"/>
       <c r="H1"/>
     </row>
-    <row r="2" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A2" s="5">
         <v>1</v>
       </c>
@@ -830,7 +827,7 @@
       <c r="F2"/>
       <c r="H2"/>
     </row>
-    <row r="3" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A3" s="5">
         <v>2</v>
       </c>
@@ -849,7 +846,7 @@
       <c r="F3"/>
       <c r="H3"/>
     </row>
-    <row r="4" spans="1:8" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" ht="20" x14ac:dyDescent="0.35">
       <c r="A4" s="8">
         <v>3</v>
       </c>
@@ -868,7 +865,7 @@
       <c r="F4"/>
       <c r="H4"/>
     </row>
-    <row r="5" spans="1:8" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" ht="20" x14ac:dyDescent="0.35">
       <c r="A5" s="5">
         <v>4</v>
       </c>
@@ -887,7 +884,7 @@
       <c r="F5"/>
       <c r="H5"/>
     </row>
-    <row r="6" spans="1:8" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" ht="20" x14ac:dyDescent="0.35">
       <c r="A6" s="5">
         <v>5</v>
       </c>
@@ -907,7 +904,7 @@
       <c r="G6"/>
       <c r="H6"/>
     </row>
-    <row r="7" spans="1:8" ht="19.2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" s="8">
         <v>6</v>
       </c>
@@ -927,7 +924,7 @@
       <c r="G7"/>
       <c r="H7"/>
     </row>
-    <row r="8" spans="1:8" ht="19.2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" ht="19" x14ac:dyDescent="0.35">
       <c r="A8" s="5">
         <v>7</v>
       </c>
@@ -946,7 +943,7 @@
       <c r="F8"/>
       <c r="H8"/>
     </row>
-    <row r="9" spans="1:8" ht="19.2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" s="5">
         <v>8</v>
       </c>
@@ -965,7 +962,7 @@
       <c r="F9"/>
       <c r="H9"/>
     </row>
-    <row r="10" spans="1:8" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" ht="20" x14ac:dyDescent="0.35">
       <c r="A10" s="8">
         <v>9</v>
       </c>
@@ -984,7 +981,7 @@
       <c r="F10"/>
       <c r="H10"/>
     </row>
-    <row r="11" spans="1:8" ht="19.2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" s="5">
         <v>10</v>
       </c>
@@ -1003,7 +1000,7 @@
       <c r="F11"/>
       <c r="H11"/>
     </row>
-    <row r="12" spans="1:8" ht="19.2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" s="5">
         <v>11</v>
       </c>
@@ -1022,7 +1019,7 @@
       <c r="F12"/>
       <c r="H12"/>
     </row>
-    <row r="13" spans="1:8" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" ht="20" x14ac:dyDescent="0.35">
       <c r="A13" s="8">
         <v>12</v>
       </c>
@@ -1041,7 +1038,7 @@
       <c r="F13"/>
       <c r="H13"/>
     </row>
-    <row r="14" spans="1:8" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" ht="20" x14ac:dyDescent="0.35">
       <c r="A14" s="5">
         <v>13</v>
       </c>
@@ -1060,7 +1057,7 @@
       <c r="F14"/>
       <c r="H14"/>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" s="5">
         <v>14</v>
       </c>
@@ -1080,7 +1077,7 @@
       <c r="G15"/>
       <c r="H15"/>
     </row>
-    <row r="16" spans="1:8" ht="19.2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" s="8">
         <v>15</v>
       </c>
@@ -1099,7 +1096,7 @@
       <c r="F16"/>
       <c r="H16"/>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A17" s="5">
         <v>16</v>
       </c>
@@ -1118,7 +1115,7 @@
       <c r="F17"/>
       <c r="H17"/>
     </row>
-    <row r="18" spans="1:8" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" ht="20" x14ac:dyDescent="0.35">
       <c r="A18" s="5">
         <v>17</v>
       </c>
@@ -1137,7 +1134,7 @@
       <c r="F18"/>
       <c r="H18"/>
     </row>
-    <row r="19" spans="1:8" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" ht="20" x14ac:dyDescent="0.35">
       <c r="A19" s="5">
         <v>18</v>
       </c>
@@ -1156,7 +1153,7 @@
       <c r="F19"/>
       <c r="H19"/>
     </row>
-    <row r="20" spans="1:8" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" ht="20" x14ac:dyDescent="0.35">
       <c r="A20" s="5">
         <v>19</v>
       </c>
@@ -1176,7 +1173,7 @@
       <c r="G20"/>
       <c r="H20"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A21" s="5">
         <v>20</v>
       </c>
@@ -1193,7 +1190,7 @@
       <c r="F21"/>
       <c r="H21"/>
     </row>
-    <row r="22" spans="1:8" ht="19.2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A22" s="5">
         <v>21</v>
       </c>
@@ -1208,7 +1205,7 @@
       <c r="F22"/>
       <c r="H22"/>
     </row>
-    <row r="23" spans="1:8" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" ht="20" x14ac:dyDescent="0.35">
       <c r="A23" s="5">
         <v>22</v>
       </c>
@@ -1228,7 +1225,7 @@
       <c r="G23" s="10"/>
       <c r="H23"/>
     </row>
-    <row r="24" spans="1:8" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" ht="20" x14ac:dyDescent="0.35">
       <c r="A24" s="5">
         <v>23</v>
       </c>
@@ -1247,7 +1244,7 @@
       <c r="F24"/>
       <c r="H24"/>
     </row>
-    <row r="25" spans="1:8" ht="19.2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" ht="19" x14ac:dyDescent="0.35">
       <c r="A25" s="5">
         <v>24</v>
       </c>
@@ -1264,8 +1261,8 @@
         <v>53</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A26" s="11">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A26" s="5">
         <v>25</v>
       </c>
       <c r="B26" s="9" t="s">
@@ -1277,10 +1274,10 @@
       <c r="D26" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="E26" s="12"/>
-    </row>
-    <row r="27" spans="1:8" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A27" s="11">
+      <c r="E26" s="11"/>
+    </row>
+    <row r="27" spans="1:8" ht="20" x14ac:dyDescent="0.35">
+      <c r="A27" s="5">
         <v>26</v>
       </c>
       <c r="B27" s="9" t="s">
@@ -1292,13 +1289,13 @@
       <c r="D27" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="E27" s="12"/>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A28" s="11">
+      <c r="E27" s="11"/>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A28" s="5">
         <v>27</v>
       </c>
-      <c r="B28" s="13" t="s">
+      <c r="B28" s="12" t="s">
         <v>10</v>
       </c>
       <c r="C28" s="8" t="s">
@@ -1307,13 +1304,13 @@
       <c r="D28" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="E28" s="12"/>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A29" s="11">
+      <c r="E28" s="11"/>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A29" s="5">
         <v>28</v>
       </c>
-      <c r="B29" s="13" t="s">
+      <c r="B29" s="12" t="s">
         <v>15</v>
       </c>
       <c r="C29" s="8" t="s">
@@ -1322,14 +1319,23 @@
       <c r="D29" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="E29" s="12"/>
+      <c r="E29" s="11"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D25" xr:uid="{A667A326-1335-4EA3-87C0-BA97F18477A6}"/>
+  <autoFilter ref="A1:D29" xr:uid="{A667A326-1335-4EA3-87C0-BA97F18477A6}"/>
   <hyperlinks>
     <hyperlink ref="C2" r:id="rId1" display="mailto:Eduardo.Vela@pmi.com" xr:uid="{579A2D25-234C-47BB-9396-335425B8E1F3}"/>
     <hyperlink ref="C3" r:id="rId2" display="mailto:JoseRaul.Rodriguez@pmi.com" xr:uid="{52DCC8FA-0268-4045-9647-B4BA2938FBDD}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter>
+    <oddFooter>&amp;C_x000D_&amp;1#&amp;"Aptos"&amp;8&amp;K000000 Public</oddFooter>
+  </headerFooter>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{7bce0314-66d2-465d-a4b8-04cf0abcda4d}" enabled="1" method="Privileged" siteId="{8b86a65e-3c3a-4406-8ac3-19a6b5cc52bc}" contentBits="2" removed="0"/>
+</clbl:labelList>
 </file>